--- a/Data/Student_Records.xlsx
+++ b/Data/Student_Records.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Belal\Antigravity workspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Belal\Antigravity workspace\CSE-412\EWU-Portal-System-main\EWU-Portal-System-main\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF4D2D8-43DB-4D14-9D89-F14900E512EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0AB2DB-11BB-4945-9195-590F7E6B450D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,9 +202,6 @@
     <t>belal.60466046.3@gmail.com</t>
   </si>
   <si>
-    <t>2023-2-80-286</t>
-  </si>
-  <si>
     <t>Nusrat Jahan</t>
   </si>
   <si>
@@ -245,6 +242,9 @@
   </si>
   <si>
     <t>CSE103:A,MAT101:F,ENG101:D</t>
+  </si>
+  <si>
+    <t>2023-2-60-286</t>
   </si>
 </sst>
 </file>
@@ -784,7 +784,7 @@
         <v>38</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>44</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>46</v>
@@ -847,7 +847,7 @@
         <v>38</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.3">
@@ -910,33 +910,33 @@
         <v>38</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>29</v>
@@ -945,10 +945,10 @@
         <v>29</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>32</v>
@@ -961,19 +961,19 @@
         <v>34</v>
       </c>
       <c r="Q5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="S5" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
